--- a/results/trace_final20_temp06_seed42_game-rl-qwen25vl7b_20260714T162908Z_results.xlsx
+++ b/results/trace_final20_temp06_seed42_game-rl-qwen25vl7b_20260714T162908Z_results.xlsx
@@ -430,15 +430,6 @@
   </sheetPr>
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -565,7 +556,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>75.23584905660378</v>
+        <v>75.31446540880503</v>
       </c>
       <c r="F4" t="n">
         <v>1272</v>
@@ -1169,18 +1160,6 @@
   </sheetPr>
   <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="70" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1367,7 +1346,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>75.23584905660378</v>
+        <v>75.31446540880503</v>
       </c>
       <c r="I4" t="n">
         <v>1272</v>
@@ -2207,20 +2186,6 @@
   </sheetPr>
   <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3297,10 +3262,6 @@
   </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/results/trace_final20_temp06_seed42_game-rl-qwen25vl7b_20260714T162908Z_results.xlsx
+++ b/results/trace_final20_temp06_seed42_game-rl-qwen25vl7b_20260714T162908Z_results.xlsx
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>19.17808219178082</v>
+        <v>21.4041095890411</v>
       </c>
       <c r="F9" t="n">
         <v>1168</v>
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>19.17808219178082</v>
+        <v>21.4041095890411</v>
       </c>
       <c r="I9" t="n">
         <v>1168</v>
